--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -1102,7 +1102,7 @@
     <t>0.0000,0.0218,0.4324,0.5818</t>
   </si>
   <si>
-    <t>0.0000,0.0077,0.9776,0.0038</t>
+    <t>0.0000,0.0077,0.9777,0.0038</t>
   </si>
   <si>
     <t>0.0004,0.0051,0.2382,0.9796</t>
@@ -1147,7 +1147,7 @@
     <t>0.0004,0.0214,0.9874,0.0007</t>
   </si>
   <si>
-    <t>0.0001,0.0197,0.9979,0.0000</t>
+    <t>0.0001,0.0196,0.9979,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.2349,0.9458,0.0024</t>
@@ -1222,7 +1222,7 @@
     <t>0.0007,0.0024,0.2901,0.9833</t>
   </si>
   <si>
-    <t>0.0000,0.0122,0.4505,0.6830</t>
+    <t>0.0000,0.0122,0.4505,0.6831</t>
   </si>
   <si>
     <t>0.0000,0.0043,0.9420,0.0242</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -826,25 +826,25 @@
     <t>0,1,0,0</t>
   </si>
   <si>
-    <t>1,0,0,0</t>
-  </si>
-  <si>
-    <t>0.0002,0.0505,0.5163,0.5008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0432,0.6726,0.1488</t>
-  </si>
-  <si>
-    <t>0.0000,0.0404,0.2680,0.7587</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.0002,0.0504,0.5161,0.5014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0432,0.6726,0.1489</t>
+  </si>
+  <si>
+    <t>0.0000,0.0403,0.2680,0.7589</t>
   </si>
   <si>
     <t>0.0001,0.0321,0.8849,0.0267</t>
   </si>
   <si>
-    <t>0.0000,0.0081,0.8614,0.0849</t>
-  </si>
-  <si>
-    <t>0.0000,0.0081,0.7519,0.2174</t>
+    <t>0.0000,0.0081,0.8614,0.0850</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,0.7519,0.2176</t>
   </si>
   <si>
     <t>0.0000,0.0045,0.9672,0.0096</t>
@@ -853,19 +853,19 @@
     <t>0.0000,0.0029,0.9933,0.0009</t>
   </si>
   <si>
-    <t>0.0000,0.0213,0.0383,0.9924</t>
-  </si>
-  <si>
-    <t>0.0000,0.0121,0.5338,0.5176</t>
+    <t>0.0000,0.0212,0.0383,0.9924</t>
+  </si>
+  <si>
+    <t>0.0000,0.0121,0.5336,0.5179</t>
   </si>
   <si>
     <t>0.0000,0.0030,0.9876,0.0025</t>
   </si>
   <si>
-    <t>0.0000,0.0074,0.8385,0.1109</t>
-  </si>
-  <si>
-    <t>0.0002,0.0385,0.9755,0.0019</t>
+    <t>0.0000,0.0073,0.8384,0.1111</t>
+  </si>
+  <si>
+    <t>0.0002,0.0385,0.9754,0.0019</t>
   </si>
   <si>
     <t>0.0001,0.0723,0.9949,0.0001</t>
@@ -880,13 +880,13 @@
     <t>0.0002,0.0169,0.9898,0.0006</t>
   </si>
   <si>
-    <t>0.0001,0.8164,0.6072,0.0293</t>
+    <t>0.0001,0.8163,0.6071,0.0293</t>
   </si>
   <si>
     <t>0.0001,0.1631,0.9404,0.0036</t>
   </si>
   <si>
-    <t>0.0001,0.6466,0.0952,0.7699</t>
+    <t>0.0001,0.6461,0.0951,0.7704</t>
   </si>
   <si>
     <t>0.0001,0.0502,0.9743,0.0016</t>
@@ -898,7 +898,7 @@
     <t>0.0002,0.0218,0.9918,0.0004</t>
   </si>
   <si>
-    <t>0.0002,0.0457,0.9941,0.0001</t>
+    <t>0.0002,0.0457,0.9941,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.0038,0.9993,0.0000</t>
@@ -916,28 +916,28 @@
     <t>0.0000,0.0019,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.1254,0.9170,0.0083</t>
-  </si>
-  <si>
-    <t>0.0000,0.0451,0.4773,0.5289</t>
+    <t>0.0002,0.1253,0.9169,0.0083</t>
+  </si>
+  <si>
+    <t>0.0000,0.0451,0.4771,0.5293</t>
   </si>
   <si>
     <t>0.0000,0.0032,0.9988,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.1358,0.9857,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0150,0.7750,0.1458</t>
+    <t>0.0001,0.1357,0.9857,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0150,0.7750,0.1459</t>
   </si>
   <si>
     <t>0.0000,0.0146,0.9515,0.0104</t>
   </si>
   <si>
-    <t>0.0002,0.5315,0.6723,0.0428</t>
-  </si>
-  <si>
-    <t>0.0001,0.2556,0.6674,0.0893</t>
+    <t>0.0002,0.5313,0.6722,0.0429</t>
+  </si>
+  <si>
+    <t>0.0001,0.2554,0.6673,0.0894</t>
   </si>
   <si>
     <t>0.0000,0.9147,0.9839,0.0000</t>
@@ -952,22 +952,22 @@
     <t>0.0009,0.1058,0.9799,0.0004</t>
   </si>
   <si>
-    <t>0.0000,0.2062,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9905,0.9111,0.0000</t>
+    <t>0.0000,0.2063,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9110,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0188,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.1979,0.6560,0.0873</t>
-  </si>
-  <si>
-    <t>0.0000,0.9964,0.3396,0.0036</t>
-  </si>
-  <si>
-    <t>0.0001,0.9940,0.6415,0.0005</t>
+    <t>0.0001,0.1977,0.6559,0.0874</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.3395,0.0036</t>
+  </si>
+  <si>
+    <t>0.0001,0.9940,0.6416,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.9967,0.4582,0.0009</t>
@@ -976,7 +976,7 @@
     <t>0.0000,0.0216,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.1220,0.9988,0.0000</t>
+    <t>0.0000,0.1222,0.9988,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.0085,0.9993,0.0000</t>
@@ -991,13 +991,13 @@
     <t>0.0000,0.0144,0.9992,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0103,0.9132,0.0314</t>
+    <t>0.0000,0.0103,0.9131,0.0315</t>
   </si>
   <si>
     <t>0.0000,0.0037,0.9811,0.0043</t>
   </si>
   <si>
-    <t>0.0000,0.0185,0.7206,0.2210</t>
+    <t>0.0000,0.0185,0.7205,0.2212</t>
   </si>
   <si>
     <t>0.0000,0.0039,0.9969,0.0003</t>
@@ -1006,7 +1006,7 @@
     <t>0.0000,0.0034,0.9850,0.0033</t>
   </si>
   <si>
-    <t>0.0000,0.0029,0.9400,0.0311</t>
+    <t>0.0000,0.0029,0.9399,0.0311</t>
   </si>
   <si>
     <t>0.0000,0.0036,0.9918,0.0012</t>
@@ -1027,25 +1027,25 @@
     <t>0.0000,0.0086,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.6107,0.8380,0.0077</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.5920,0.0004</t>
+    <t>0.0000,0.6108,0.8379,0.0077</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.5919,0.0004</t>
   </si>
   <si>
     <t>0.0004,0.0385,0.9367,0.0108</t>
   </si>
   <si>
-    <t>0.0002,0.2110,0.8115,0.0344</t>
-  </si>
-  <si>
-    <t>0.0001,0.0680,0.9867,0.0007</t>
+    <t>0.0002,0.2108,0.8114,0.0344</t>
+  </si>
+  <si>
+    <t>0.0001,0.0679,0.9867,0.0007</t>
   </si>
   <si>
     <t>0.0000,0.7495,0.9983,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.4905,0.9992,0.0000</t>
+    <t>0.0000,0.4906,0.9992,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9948,0.9906,0.0000</t>
@@ -1054,34 +1054,34 @@
     <t>0.0000,0.8691,0.9942,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0135,0.5313,0.5005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0533,0.6288,0.1816</t>
-  </si>
-  <si>
-    <t>0.0001,0.0393,0.7346,0.0979</t>
-  </si>
-  <si>
-    <t>0.0000,0.0130,0.6210,0.3350</t>
-  </si>
-  <si>
-    <t>0.0000,0.0434,0.3791,0.5556</t>
-  </si>
-  <si>
-    <t>0.0000,0.0262,0.5043,0.4285</t>
+    <t>0.0000,0.0134,0.5311,0.5010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0533,0.6288,0.1817</t>
+  </si>
+  <si>
+    <t>0.0001,0.0393,0.7345,0.0981</t>
+  </si>
+  <si>
+    <t>0.0000,0.0130,0.6210,0.3351</t>
+  </si>
+  <si>
+    <t>0.0000,0.0433,0.3790,0.5560</t>
+  </si>
+  <si>
+    <t>0.0000,0.0261,0.5042,0.4288</t>
   </si>
   <si>
     <t>0.0000,0.9581,0.9917,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.4274,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.6326,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1805,0.9996,0.0000</t>
+    <t>0.0000,0.4275,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6327,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1806,0.9996,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9427,0.9989,0.0000</t>
@@ -1090,49 +1090,49 @@
     <t>0.0000,0.9361,0.9829,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0182,0.2528,0.8604</t>
-  </si>
-  <si>
-    <t>0.0000,0.0132,0.8103,0.1146</t>
-  </si>
-  <si>
-    <t>0.0001,0.0061,0.0635,0.9959</t>
-  </si>
-  <si>
-    <t>0.0000,0.0218,0.4324,0.5818</t>
-  </si>
-  <si>
-    <t>0.0000,0.0077,0.9777,0.0038</t>
+    <t>0.0000,0.0182,0.2528,0.8605</t>
+  </si>
+  <si>
+    <t>0.0000,0.0132,0.8103,0.1147</t>
+  </si>
+  <si>
+    <t>0.0001,0.0061,0.0634,0.9959</t>
+  </si>
+  <si>
+    <t>0.0000,0.0218,0.4324,0.5820</t>
+  </si>
+  <si>
+    <t>0.0000,0.0077,0.9776,0.0038</t>
   </si>
   <si>
     <t>0.0004,0.0051,0.2382,0.9796</t>
   </si>
   <si>
-    <t>0.0000,0.0076,0.9378,0.0228</t>
-  </si>
-  <si>
-    <t>0.0281,0.0049,0.6429,0.6101</t>
-  </si>
-  <si>
-    <t>0.0000,0.0058,0.8311,0.1393</t>
+    <t>0.0000,0.0076,0.9377,0.0228</t>
+  </si>
+  <si>
+    <t>0.0280,0.0049,0.6430,0.6105</t>
+  </si>
+  <si>
+    <t>0.0000,0.0058,0.8311,0.1394</t>
   </si>
   <si>
     <t>0.0001,0.0036,0.0605,0.9957</t>
   </si>
   <si>
-    <t>0.0000,0.0045,0.9258,0.0362</t>
-  </si>
-  <si>
-    <t>0.0001,0.0056,0.0943,0.9863</t>
-  </si>
-  <si>
-    <t>0.0000,0.0146,0.1073,0.9685</t>
-  </si>
-  <si>
-    <t>0.0017,0.0017,0.3006,0.9830</t>
-  </si>
-  <si>
-    <t>0.0000,0.0151,0.1460,0.9405</t>
+    <t>0.0000,0.0045,0.9259,0.0362</t>
+  </si>
+  <si>
+    <t>0.0001,0.0056,0.0942,0.9863</t>
+  </si>
+  <si>
+    <t>0.0000,0.0146,0.1073,0.9686</t>
+  </si>
+  <si>
+    <t>0.0017,0.0017,0.3004,0.9830</t>
+  </si>
+  <si>
+    <t>0.0000,0.0150,0.1459,0.9406</t>
   </si>
   <si>
     <t>0.0000,0.0047,0.9812,0.0037</t>
@@ -1144,7 +1144,7 @@
     <t>0.0001,0.0107,0.9983,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0214,0.9874,0.0007</t>
+    <t>0.0004,0.0214,0.9873,0.0007</t>
   </si>
   <si>
     <t>0.0001,0.0196,0.9979,0.0000</t>
@@ -1153,22 +1153,22 @@
     <t>0.0000,0.2349,0.9458,0.0024</t>
   </si>
   <si>
-    <t>0.0000,0.8944,0.7167,0.0075</t>
-  </si>
-  <si>
-    <t>0.0001,0.7098,0.2826,0.2614</t>
-  </si>
-  <si>
-    <t>0.0001,0.2875,0.8673,0.0106</t>
-  </si>
-  <si>
-    <t>0.0000,0.3993,0.9582,0.0009</t>
+    <t>0.0000,0.8943,0.7166,0.0075</t>
+  </si>
+  <si>
+    <t>0.0001,0.7095,0.2825,0.2617</t>
+  </si>
+  <si>
+    <t>0.0001,0.2874,0.8672,0.0107</t>
+  </si>
+  <si>
+    <t>0.0000,0.3992,0.9582,0.0009</t>
   </si>
   <si>
     <t>0.0000,0.9123,0.7954,0.0031</t>
   </si>
   <si>
-    <t>0.0001,0.1340,0.8622,0.0180</t>
+    <t>0.0001,0.1339,0.8621,0.0180</t>
   </si>
   <si>
     <t>0.0001,0.1029,0.9819,0.0006</t>
@@ -1177,19 +1177,19 @@
     <t>0.0002,0.0697,0.9917,0.0002</t>
   </si>
   <si>
-    <t>0.0002,0.2346,0.9749,0.0006</t>
+    <t>0.0002,0.2344,0.9749,0.0006</t>
   </si>
   <si>
     <t>0.0001,0.1317,0.9777,0.0007</t>
   </si>
   <si>
-    <t>0.0002,0.1565,0.8612,0.0439</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.2795,0.0038</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.3202,0.0031</t>
+    <t>0.0002,0.1562,0.8611,0.0440</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.2794,0.0038</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.3201,0.0031</t>
   </si>
   <si>
     <t>0.0001,0.7719,0.9012,0.0014</t>
@@ -1198,40 +1198,40 @@
     <t>0.0000,0.9961,0.7288,0.0002</t>
   </si>
   <si>
-    <t>0.0001,0.6364,0.7567,0.0196</t>
-  </si>
-  <si>
-    <t>0.0001,0.1084,0.8641,0.0224</t>
+    <t>0.0001,0.6361,0.7567,0.0196</t>
+  </si>
+  <si>
+    <t>0.0001,0.1083,0.8640,0.0225</t>
   </si>
   <si>
     <t>0.0001,0.0932,0.9187,0.0089</t>
   </si>
   <si>
-    <t>0.0000,0.0105,0.1711,0.9470</t>
-  </si>
-  <si>
-    <t>0.0001,0.0320,0.1354,0.9370</t>
-  </si>
-  <si>
-    <t>0.0000,0.0124,0.3245,0.8090</t>
-  </si>
-  <si>
-    <t>0.0001,0.0144,0.7823,0.1342</t>
-  </si>
-  <si>
-    <t>0.0007,0.0024,0.2901,0.9833</t>
-  </si>
-  <si>
-    <t>0.0000,0.0122,0.4505,0.6831</t>
-  </si>
-  <si>
-    <t>0.0000,0.0043,0.9420,0.0242</t>
+    <t>0.0000,0.0105,0.1710,0.9471</t>
+  </si>
+  <si>
+    <t>0.0001,0.0320,0.1353,0.9371</t>
+  </si>
+  <si>
+    <t>0.0000,0.0124,0.3243,0.8093</t>
+  </si>
+  <si>
+    <t>0.0001,0.0144,0.7822,0.1343</t>
+  </si>
+  <si>
+    <t>0.0007,0.0024,0.2899,0.9833</t>
+  </si>
+  <si>
+    <t>0.0000,0.0122,0.4502,0.6835</t>
+  </si>
+  <si>
+    <t>0.0000,0.0043,0.9420,0.0243</t>
   </si>
   <si>
     <t>0.0000,0.0043,0.9820,0.0035</t>
   </si>
   <si>
-    <t>0.0000,0.3992,0.9971,0.0000</t>
+    <t>0.0000,0.3993,0.9971,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.3354,0.9993,0.0000</t>
@@ -1252,19 +1252,19 @@
     <t>0.0002,0.0081,0.9961,0.0003</t>
   </si>
   <si>
-    <t>0.0003,0.2190,0.9626,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.0080,0.7294,0.2208</t>
-  </si>
-  <si>
-    <t>0.0000,0.1543,0.3010,0.4800</t>
-  </si>
-  <si>
-    <t>0.0001,0.0678,0.6139,0.1676</t>
-  </si>
-  <si>
-    <t>0.0000,0.0262,0.2912,0.7222</t>
+    <t>0.0003,0.2189,0.9626,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0080,0.7292,0.2212</t>
+  </si>
+  <si>
+    <t>0.0000,0.1542,0.3009,0.4802</t>
+  </si>
+  <si>
+    <t>0.0001,0.0678,0.6138,0.1677</t>
+  </si>
+  <si>
+    <t>0.0000,0.0262,0.2910,0.7225</t>
   </si>
   <si>
     <t>0.0000,0.9676,0.9867,0.0000</t>
@@ -1273,7 +1273,7 @@
     <t>0.0000,0.0047,0.9668,0.0091</t>
   </si>
   <si>
-    <t>0.0000,0.0353,0.9426,0.0083</t>
+    <t>0.0000,0.0353,0.9426,0.0084</t>
   </si>
   <si>
     <t>0.0000,0.0072,0.9754,0.0046</t>
@@ -1282,7 +1282,7 @@
     <t>0.0000,0.0208,0.9731,0.0031</t>
   </si>
   <si>
-    <t>0.0001,0.0215,0.6207,0.3323</t>
+    <t>0.0001,0.0215,0.6206,0.3326</t>
   </si>
   <si>
     <t>0.0004,0.0006,0.9943,0.0051</t>
@@ -1297,28 +1297,28 @@
     <t>0.0003,0.0112,0.9821,0.0024</t>
   </si>
   <si>
-    <t>0.0001,0.0406,0.9027,0.0245</t>
-  </si>
-  <si>
-    <t>0.0000,0.0298,0.9110,0.0206</t>
+    <t>0.0001,0.0405,0.9027,0.0245</t>
+  </si>
+  <si>
+    <t>0.0000,0.0297,0.9110,0.0206</t>
   </si>
   <si>
     <t>0.0001,0.0316,0.9063,0.0195</t>
   </si>
   <si>
-    <t>0.0002,0.1193,0.8804,0.0165</t>
-  </si>
-  <si>
-    <t>0.0000,0.1670,0.7059,0.0735</t>
-  </si>
-  <si>
-    <t>0.0001,0.0614,0.8939,0.0192</t>
-  </si>
-  <si>
-    <t>0.0003,0.2800,0.7475,0.0443</t>
-  </si>
-  <si>
-    <t>0.0000,0.0143,0.5805,0.4279</t>
+    <t>0.0002,0.1192,0.8803,0.0166</t>
+  </si>
+  <si>
+    <t>0.0000,0.1669,0.7058,0.0736</t>
+  </si>
+  <si>
+    <t>0.0001,0.0614,0.8938,0.0192</t>
+  </si>
+  <si>
+    <t>0.0003,0.2797,0.7473,0.0444</t>
+  </si>
+  <si>
+    <t>0.0000,0.0143,0.5805,0.4282</t>
   </si>
   <si>
     <t>0.0000,0.0103,0.0511,0.9949</t>
@@ -1330,22 +1330,22 @@
     <t>0.0000,0.0034,0.9930,0.0009</t>
   </si>
   <si>
-    <t>0.0000,0.0121,0.8356,0.0902</t>
-  </si>
-  <si>
-    <t>0.0000,0.0207,0.6014,0.3461</t>
-  </si>
-  <si>
-    <t>0.0000,0.0125,0.7883,0.1349</t>
+    <t>0.0000,0.0121,0.8356,0.0903</t>
+  </si>
+  <si>
+    <t>0.0000,0.0207,0.6014,0.3464</t>
+  </si>
+  <si>
+    <t>0.0000,0.0125,0.7882,0.1351</t>
   </si>
   <si>
     <t>0.0000,0.0034,0.9805,0.0047</t>
   </si>
   <si>
-    <t>0.0000,0.1321,0.3100,0.6265</t>
-  </si>
-  <si>
-    <t>0.0001,0.1539,0.7891,0.0437</t>
+    <t>0.0000,0.1320,0.3099,0.6268</t>
+  </si>
+  <si>
+    <t>0.0001,0.1538,0.7890,0.0438</t>
   </si>
   <si>
     <t>0.0001,0.0190,0.9869,0.0009</t>
@@ -1363,7 +1363,7 @@
     <t>0.0000,0.0057,0.9886,0.0014</t>
   </si>
   <si>
-    <t>0.0000,0.0147,0.8454,0.0677</t>
+    <t>0.0000,0.0147,0.8453,0.0678</t>
   </si>
   <si>
     <t>0.0000,0.0047,0.9990,0.0000</t>
@@ -1393,22 +1393,22 @@
     <t>0.0001,0.0148,0.9987,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.1679,0.9853,0.0003</t>
+    <t>0.0002,0.1678,0.9853,0.0003</t>
   </si>
   <si>
     <t>0.0002,0.0214,0.9944,0.0002</t>
   </si>
   <si>
-    <t>0.0003,0.1828,0.9751,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.1312,0.9909,0.0001</t>
+    <t>0.0003,0.1827,0.9750,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.1311,0.9909,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0568,0.9960,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.0608,0.9916,0.0002</t>
+    <t>0.0004,0.0607,0.9916,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.1099,0.9770,0.0010</t>
@@ -1417,10 +1417,10 @@
     <t>0.0005,0.3654,0.9578,0.0010</t>
   </si>
   <si>
-    <t>0.0001,0.1117,0.2106,0.8770</t>
-  </si>
-  <si>
-    <t>0.0001,0.0690,0.8688,0.0273</t>
+    <t>0.0001,0.1114,0.2105,0.8772</t>
+  </si>
+  <si>
+    <t>0.0001,0.0689,0.8687,0.0273</t>
   </si>
   <si>
     <t>0.0000,0.0266,0.9385,0.0118</t>
@@ -1429,16 +1429,16 @@
     <t>0.0000,0.0081,0.9844,0.0021</t>
   </si>
   <si>
-    <t>0.0000,0.0122,0.9443,0.0133</t>
-  </si>
-  <si>
-    <t>0.0002,0.4571,0.9471,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.0427,0.9705,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.1495,0.9650,0.0018</t>
+    <t>0.0000,0.0122,0.9443,0.0134</t>
+  </si>
+  <si>
+    <t>0.0002,0.4572,0.9471,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0427,0.9704,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.1496,0.9649,0.0018</t>
   </si>
   <si>
     <t>0.0006,0.0466,0.9880,0.0005</t>
@@ -1453,34 +1453,34 @@
     <t>0.0003,0.1622,0.9846,0.0003</t>
   </si>
   <si>
-    <t>0.0004,0.2103,0.9844,0.0002</t>
+    <t>0.0004,0.2104,0.9844,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0191,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.2253,0.9929,0.0000</t>
+    <t>0.0002,0.2254,0.9929,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0029,0.9838,0.0042</t>
   </si>
   <si>
-    <t>0.0000,0.0069,0.9446,0.0174</t>
-  </si>
-  <si>
-    <t>0.0000,0.0187,0.4069,0.6631</t>
-  </si>
-  <si>
-    <t>0.0000,0.0114,0.0649,0.9906</t>
-  </si>
-  <si>
-    <t>0.0000,0.0118,0.6007,0.3988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0158,0.7660,0.1377</t>
-  </si>
-  <si>
-    <t>0.0000,0.0141,0.7792,0.1491</t>
+    <t>0.0000,0.0069,0.9446,0.0175</t>
+  </si>
+  <si>
+    <t>0.0000,0.0187,0.4067,0.6635</t>
+  </si>
+  <si>
+    <t>0.0000,0.0114,0.0648,0.9906</t>
+  </si>
+  <si>
+    <t>0.0000,0.0118,0.6006,0.3991</t>
+  </si>
+  <si>
+    <t>0.0000,0.0158,0.7660,0.1378</t>
+  </si>
+  <si>
+    <t>0.0000,0.0141,0.7791,0.1492</t>
   </si>
   <si>
     <t>0.0000,0.0031,0.9930,0.0010</t>
@@ -1516,7 +1516,7 @@
     <t>0.0000,0.0093,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.3142,0.9792,0.0003</t>
+    <t>0.0001,0.3141,0.9792,0.0003</t>
   </si>
   <si>
     <t>0.0005,0.0426,0.9763,0.0017</t>
@@ -1543,16 +1543,16 @@
     <t>0.0000,0.0057,0.9868,0.0020</t>
   </si>
   <si>
-    <t>0.0000,0.0268,0.6594,0.2341</t>
-  </si>
-  <si>
-    <t>0.0000,0.0179,0.3578,0.7189</t>
-  </si>
-  <si>
-    <t>0.0000,0.0284,0.6866,0.2070</t>
-  </si>
-  <si>
-    <t>0.0000,0.0249,0.9995,0.0000</t>
+    <t>0.0000,0.0268,0.6593,0.2343</t>
+  </si>
+  <si>
+    <t>0.0000,0.0179,0.3576,0.7193</t>
+  </si>
+  <si>
+    <t>0.0000,0.0284,0.6865,0.2072</t>
+  </si>
+  <si>
+    <t>0.0000,0.0250,0.9995,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0100,0.9998,0.0000</t>
@@ -1567,7 +1567,7 @@
     <t>0.0001,0.0049,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0811,0.5619,0.2177</t>
+    <t>0.0000,0.0810,0.5617,0.2179</t>
   </si>
   <si>
     <t>0.0001,0.0474,0.9757,0.0019</t>
@@ -1576,22 +1576,22 @@
     <t>0.0000,0.0208,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0310,0.6404,0.2906</t>
-  </si>
-  <si>
-    <t>0.0001,0.1266,0.8243,0.0260</t>
-  </si>
-  <si>
-    <t>0.0000,0.0219,0.3226,0.7555</t>
-  </si>
-  <si>
-    <t>0.0000,0.0039,0.1545,0.9843</t>
-  </si>
-  <si>
-    <t>0.0000,0.0316,0.2978,0.7668</t>
-  </si>
-  <si>
-    <t>0.0012,0.1439,0.9069,0.0090</t>
+    <t>0.0001,0.0310,0.6401,0.2912</t>
+  </si>
+  <si>
+    <t>0.0001,0.1265,0.8242,0.0260</t>
+  </si>
+  <si>
+    <t>0.0000,0.0218,0.3224,0.7558</t>
+  </si>
+  <si>
+    <t>0.0000,0.0039,0.1545,0.9844</t>
+  </si>
+  <si>
+    <t>0.0000,0.0315,0.2976,0.7671</t>
+  </si>
+  <si>
+    <t>0.0012,0.1438,0.9068,0.0090</t>
   </si>
 </sst>
 </file>
